--- a/dev/StructureDefinition-ph-core-practitioner.xlsx
+++ b/dev/StructureDefinition-ph-core-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-16T05:11:07+00:00</t>
+    <t>2026-03-16T07:24:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/StructureDefinition-ph-core-practitioner.xlsx
+++ b/dev/StructureDefinition-ph-core-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-16T07:24:26+00:00</t>
+    <t>2026-03-16T20:48:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/StructureDefinition-ph-core-practitioner.xlsx
+++ b/dev/StructureDefinition-ph-core-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-16T20:48:05+00:00</t>
+    <t>2026-03-16T20:59:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/StructureDefinition-ph-core-practitioner.xlsx
+++ b/dev/StructureDefinition-ph-core-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-16T20:59:47+00:00</t>
+    <t>2026-03-16T21:16:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/StructureDefinition-ph-core-practitioner.xlsx
+++ b/dev/StructureDefinition-ph-core-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-16T21:16:15+00:00</t>
+    <t>2026-03-16T21:44:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/StructureDefinition-ph-core-practitioner.xlsx
+++ b/dev/StructureDefinition-ph-core-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-16T21:44:19+00:00</t>
+    <t>2026-03-16T21:58:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/StructureDefinition-ph-core-practitioner.xlsx
+++ b/dev/StructureDefinition-ph-core-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-16T21:58:37+00:00</t>
+    <t>2026-03-16T22:06:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/StructureDefinition-ph-core-practitioner.xlsx
+++ b/dev/StructureDefinition-ph-core-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-16T22:06:54+00:00</t>
+    <t>2026-03-16T22:26:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/StructureDefinition-ph-core-practitioner.xlsx
+++ b/dev/StructureDefinition-ph-core-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-16T22:26:22+00:00</t>
+    <t>2026-03-19T20:53:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/StructureDefinition-ph-core-practitioner.xlsx
+++ b/dev/StructureDefinition-ph-core-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-19T20:53:49+00:00</t>
+    <t>2026-03-19T21:27:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/StructureDefinition-ph-core-practitioner.xlsx
+++ b/dev/StructureDefinition-ph-core-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-19T21:27:42+00:00</t>
+    <t>2026-04-08T04:20:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/StructureDefinition-ph-core-practitioner.xlsx
+++ b/dev/StructureDefinition-ph-core-practitioner.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$27</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$35</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1015" uniqueCount="269">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1305" uniqueCount="295">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0</t>
+    <t>0.2.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-08T04:20:57+00:00</t>
+    <t>2026-04-10T05:32:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -591,7 +591,7 @@
     <t>Practitioner.address</t>
   </si>
   <si>
-    <t xml:space="preserve">Address {http://doh.gov.ph/fhir/ph-core/StructureDefinition/ph-core-address|Address}
+    <t xml:space="preserve">Address {http://doh.gov.ph/fhir/ph-core/StructureDefinition/ph-core-address}
 </t>
   </si>
   <si>
@@ -801,6 +801,74 @@
     <t>./Qualifications.Value</t>
   </si>
   <si>
+    <t>Practitioner.qualification.code.id</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification.code.extension</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value:url}
+</t>
+  </si>
+  <si>
+    <t>Extensions are always sliced by (at least) url</t>
+  </si>
+  <si>
+    <t>open</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification.code.coding</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coding
+</t>
+  </si>
+  <si>
+    <t>Code defined by a terminology system</t>
+  </si>
+  <si>
+    <t>A reference to a code defined by a terminology system.</t>
+  </si>
+  <si>
+    <t>Codes may be defined very casually in enumerations, or code lists, up to very formal definitions such as SNOMED CT - see the HL7 v3 Core Principles for more information.  Ordering of codings is undefined and SHALL NOT be used to infer meaning. Generally, at most only one of the coding values will be labeled as UserSelected = true.</t>
+  </si>
+  <si>
+    <t>Allows for alternative encodings within a code system, and translations to other code systems.</t>
+  </si>
+  <si>
+    <t>CodeableConcept.coding</t>
+  </si>
+  <si>
+    <t>C*E.1-8, C*E.10-22</t>
+  </si>
+  <si>
+    <t>union(., ./translation)</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification.code.text</t>
+  </si>
+  <si>
+    <t>Plain text representation of the concept</t>
+  </si>
+  <si>
+    <t>A human language representation of the concept as seen/selected/uttered by the user who entered the data and/or which represents the intended meaning of the user.</t>
+  </si>
+  <si>
+    <t>Very often the text is the same as a displayName of one of the codings.</t>
+  </si>
+  <si>
+    <t>The codes from the terminologies do not always capture the correct meaning with all the nuances of the human using them, or sometimes there is no appropriate code at all. In these cases, the text is used to capture the full meaning of the source.</t>
+  </si>
+  <si>
+    <t>CodeableConcept.text</t>
+  </si>
+  <si>
+    <t>C*E.9. But note many systems use C*E.2 for this</t>
+  </si>
+  <si>
+    <t>./originalText[mediaType/code="text/plain"]/data</t>
+  </si>
+  <si>
     <t>Practitioner.qualification.period</t>
   </si>
   <si>
@@ -861,6 +929,18 @@
   </si>
   <si>
     <t>./Languages.LanguageSpokenCode</t>
+  </si>
+  <si>
+    <t>Practitioner.communication.id</t>
+  </si>
+  <si>
+    <t>Practitioner.communication.extension</t>
+  </si>
+  <si>
+    <t>Practitioner.communication.coding</t>
+  </si>
+  <si>
+    <t>Practitioner.communication.text</t>
   </si>
 </sst>
 </file>
@@ -1177,7 +1257,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AN27"/>
+  <dimension ref="A1:AN35"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="34.8984375" customWidth="true" bestFit="true"/>
@@ -1190,7 +1270,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="68.703125" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="61.85546875" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1208,14 +1288,14 @@
     <col min="26" max="26" width="44.51171875" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="17.65625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="32" max="32" width="29.88671875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="26.65625" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="39.109375" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="47.515625" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="44.90625" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="31.65234375" customWidth="true" bestFit="true"/>
@@ -3857,7 +3937,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="24" hidden="true">
+    <row r="24">
       <c r="A24" t="s" s="2">
         <v>241</v>
       </c>
@@ -3876,7 +3956,7 @@
         <v>88</v>
       </c>
       <c r="H24" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="I24" t="s" s="2">
         <v>77</v>
@@ -3997,18 +4077,16 @@
         <v>77</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>250</v>
+        <v>223</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>251</v>
+        <v>224</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>252</v>
+        <v>225</v>
       </c>
       <c r="N25" s="2"/>
-      <c r="O25" t="s" s="2">
-        <v>253</v>
-      </c>
+      <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
         <v>77</v>
       </c>
@@ -4056,7 +4134,7 @@
         <v>77</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>249</v>
+        <v>226</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>78</v>
@@ -4068,16 +4146,16 @@
         <v>77</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>100</v>
+        <v>77</v>
       </c>
       <c r="AK25" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>254</v>
+        <v>227</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>255</v>
+        <v>77</v>
       </c>
       <c r="AN25" t="s" s="2">
         <v>77</v>
@@ -4085,21 +4163,21 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>256</v>
+        <v>250</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>256</v>
+        <v>250</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>77</v>
+        <v>133</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H26" t="s" s="2">
         <v>77</v>
@@ -4111,15 +4189,17 @@
         <v>77</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>257</v>
+        <v>134</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>258</v>
+        <v>135</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>259</v>
-      </c>
-      <c r="N26" s="2"/>
+        <v>229</v>
+      </c>
+      <c r="N26" t="s" s="2">
+        <v>137</v>
+      </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
         <v>77</v>
@@ -4156,37 +4236,37 @@
         <v>77</v>
       </c>
       <c r="AB26" t="s" s="2">
-        <v>77</v>
+        <v>251</v>
       </c>
       <c r="AC26" t="s" s="2">
-        <v>77</v>
+        <v>252</v>
       </c>
       <c r="AD26" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE26" t="s" s="2">
-        <v>77</v>
+        <v>253</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>256</v>
+        <v>230</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI26" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="AK26" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>260</v>
+        <v>227</v>
       </c>
       <c r="AM26" t="s" s="2">
         <v>77</v>
@@ -4195,12 +4275,12 @@
         <v>77</v>
       </c>
     </row>
-    <row r="27" hidden="true">
+    <row r="27">
       <c r="A27" t="s" s="2">
-        <v>261</v>
+        <v>254</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>261</v>
+        <v>254</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4214,28 +4294,28 @@
         <v>79</v>
       </c>
       <c r="H27" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="I27" t="s" s="2">
         <v>77</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>242</v>
+        <v>255</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>262</v>
+        <v>256</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>263</v>
+        <v>257</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>264</v>
+        <v>258</v>
       </c>
       <c r="O27" t="s" s="2">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>77</v>
@@ -4260,13 +4340,13 @@
         <v>77</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>112</v>
+        <v>77</v>
       </c>
       <c r="Y27" t="s" s="2">
-        <v>113</v>
+        <v>77</v>
       </c>
       <c r="Z27" t="s" s="2">
-        <v>114</v>
+        <v>77</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>77</v>
@@ -4284,7 +4364,7 @@
         <v>77</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>78</v>
@@ -4299,20 +4379,936 @@
         <v>100</v>
       </c>
       <c r="AK27" t="s" s="2">
+        <v>261</v>
+      </c>
+      <c r="AL27" t="s" s="2">
+        <v>262</v>
+      </c>
+      <c r="AM27" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN27" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="B28" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="C28" s="2"/>
+      <c r="D28" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E28" s="2"/>
+      <c r="F28" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G28" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H28" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="I28" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J28" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="K28" t="s" s="2">
+        <v>223</v>
+      </c>
+      <c r="L28" t="s" s="2">
+        <v>264</v>
+      </c>
+      <c r="M28" t="s" s="2">
+        <v>265</v>
+      </c>
+      <c r="N28" t="s" s="2">
         <v>266</v>
       </c>
-      <c r="AL27" t="s" s="2">
+      <c r="O28" t="s" s="2">
         <v>267</v>
       </c>
-      <c r="AM27" t="s" s="2">
+      <c r="P28" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q28" s="2"/>
+      <c r="R28" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S28" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T28" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U28" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V28" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W28" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X28" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y28" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z28" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA28" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB28" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC28" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD28" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE28" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF28" t="s" s="2">
         <v>268</v>
       </c>
-      <c r="AN27" t="s" s="2">
+      <c r="AG28" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH28" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI28" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ28" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK28" t="s" s="2">
+        <v>269</v>
+      </c>
+      <c r="AL28" t="s" s="2">
+        <v>270</v>
+      </c>
+      <c r="AM28" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN28" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="29" hidden="true">
+      <c r="A29" t="s" s="2">
+        <v>271</v>
+      </c>
+      <c r="B29" t="s" s="2">
+        <v>271</v>
+      </c>
+      <c r="C29" s="2"/>
+      <c r="D29" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E29" s="2"/>
+      <c r="F29" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G29" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H29" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I29" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J29" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K29" t="s" s="2">
+        <v>272</v>
+      </c>
+      <c r="L29" t="s" s="2">
+        <v>273</v>
+      </c>
+      <c r="M29" t="s" s="2">
+        <v>274</v>
+      </c>
+      <c r="N29" s="2"/>
+      <c r="O29" t="s" s="2">
+        <v>275</v>
+      </c>
+      <c r="P29" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q29" s="2"/>
+      <c r="R29" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S29" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T29" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U29" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V29" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W29" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X29" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y29" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z29" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA29" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB29" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC29" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD29" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE29" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF29" t="s" s="2">
+        <v>271</v>
+      </c>
+      <c r="AG29" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH29" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI29" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ29" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK29" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL29" t="s" s="2">
+        <v>276</v>
+      </c>
+      <c r="AM29" t="s" s="2">
+        <v>277</v>
+      </c>
+      <c r="AN29" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="30" hidden="true">
+      <c r="A30" t="s" s="2">
+        <v>278</v>
+      </c>
+      <c r="B30" t="s" s="2">
+        <v>278</v>
+      </c>
+      <c r="C30" s="2"/>
+      <c r="D30" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E30" s="2"/>
+      <c r="F30" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G30" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H30" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I30" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J30" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K30" t="s" s="2">
+        <v>279</v>
+      </c>
+      <c r="L30" t="s" s="2">
+        <v>280</v>
+      </c>
+      <c r="M30" t="s" s="2">
+        <v>281</v>
+      </c>
+      <c r="N30" s="2"/>
+      <c r="O30" s="2"/>
+      <c r="P30" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q30" s="2"/>
+      <c r="R30" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S30" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T30" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U30" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V30" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W30" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X30" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y30" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z30" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA30" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB30" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC30" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD30" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE30" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF30" t="s" s="2">
+        <v>278</v>
+      </c>
+      <c r="AG30" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH30" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI30" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ30" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK30" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL30" t="s" s="2">
+        <v>282</v>
+      </c>
+      <c r="AM30" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN30" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="s" s="2">
+        <v>283</v>
+      </c>
+      <c r="B31" t="s" s="2">
+        <v>283</v>
+      </c>
+      <c r="C31" s="2"/>
+      <c r="D31" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E31" s="2"/>
+      <c r="F31" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G31" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H31" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="I31" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J31" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K31" t="s" s="2">
+        <v>242</v>
+      </c>
+      <c r="L31" t="s" s="2">
+        <v>284</v>
+      </c>
+      <c r="M31" t="s" s="2">
+        <v>285</v>
+      </c>
+      <c r="N31" t="s" s="2">
+        <v>286</v>
+      </c>
+      <c r="O31" t="s" s="2">
+        <v>287</v>
+      </c>
+      <c r="P31" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q31" s="2"/>
+      <c r="R31" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S31" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T31" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U31" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V31" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W31" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X31" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="Y31" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="Z31" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="AA31" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB31" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC31" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD31" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE31" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF31" t="s" s="2">
+        <v>283</v>
+      </c>
+      <c r="AG31" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH31" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI31" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ31" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK31" t="s" s="2">
+        <v>288</v>
+      </c>
+      <c r="AL31" t="s" s="2">
+        <v>289</v>
+      </c>
+      <c r="AM31" t="s" s="2">
+        <v>290</v>
+      </c>
+      <c r="AN31" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="32" hidden="true">
+      <c r="A32" t="s" s="2">
+        <v>291</v>
+      </c>
+      <c r="B32" t="s" s="2">
+        <v>291</v>
+      </c>
+      <c r="C32" s="2"/>
+      <c r="D32" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E32" s="2"/>
+      <c r="F32" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G32" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H32" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I32" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J32" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K32" t="s" s="2">
+        <v>223</v>
+      </c>
+      <c r="L32" t="s" s="2">
+        <v>224</v>
+      </c>
+      <c r="M32" t="s" s="2">
+        <v>225</v>
+      </c>
+      <c r="N32" s="2"/>
+      <c r="O32" s="2"/>
+      <c r="P32" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q32" s="2"/>
+      <c r="R32" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S32" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T32" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U32" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V32" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W32" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X32" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y32" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z32" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA32" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB32" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC32" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD32" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE32" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF32" t="s" s="2">
+        <v>226</v>
+      </c>
+      <c r="AG32" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH32" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI32" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ32" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AK32" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL32" t="s" s="2">
+        <v>227</v>
+      </c>
+      <c r="AM32" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN32" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="33" hidden="true">
+      <c r="A33" t="s" s="2">
+        <v>292</v>
+      </c>
+      <c r="B33" t="s" s="2">
+        <v>292</v>
+      </c>
+      <c r="C33" s="2"/>
+      <c r="D33" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="E33" s="2"/>
+      <c r="F33" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G33" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H33" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I33" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J33" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K33" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="L33" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="M33" t="s" s="2">
+        <v>229</v>
+      </c>
+      <c r="N33" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="O33" s="2"/>
+      <c r="P33" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q33" s="2"/>
+      <c r="R33" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S33" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T33" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U33" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V33" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W33" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X33" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y33" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z33" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA33" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB33" t="s" s="2">
+        <v>251</v>
+      </c>
+      <c r="AC33" t="s" s="2">
+        <v>252</v>
+      </c>
+      <c r="AD33" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE33" t="s" s="2">
+        <v>253</v>
+      </c>
+      <c r="AF33" t="s" s="2">
+        <v>230</v>
+      </c>
+      <c r="AG33" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH33" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI33" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ33" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="AK33" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL33" t="s" s="2">
+        <v>227</v>
+      </c>
+      <c r="AM33" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN33" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="s" s="2">
+        <v>293</v>
+      </c>
+      <c r="B34" t="s" s="2">
+        <v>293</v>
+      </c>
+      <c r="C34" s="2"/>
+      <c r="D34" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E34" s="2"/>
+      <c r="F34" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G34" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H34" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="I34" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J34" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="K34" t="s" s="2">
+        <v>255</v>
+      </c>
+      <c r="L34" t="s" s="2">
+        <v>256</v>
+      </c>
+      <c r="M34" t="s" s="2">
+        <v>257</v>
+      </c>
+      <c r="N34" t="s" s="2">
+        <v>258</v>
+      </c>
+      <c r="O34" t="s" s="2">
+        <v>259</v>
+      </c>
+      <c r="P34" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q34" s="2"/>
+      <c r="R34" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S34" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T34" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U34" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V34" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W34" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X34" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y34" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z34" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA34" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB34" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC34" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD34" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE34" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF34" t="s" s="2">
+        <v>260</v>
+      </c>
+      <c r="AG34" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH34" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI34" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ34" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK34" t="s" s="2">
+        <v>261</v>
+      </c>
+      <c r="AL34" t="s" s="2">
+        <v>262</v>
+      </c>
+      <c r="AM34" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN34" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="s" s="2">
+        <v>294</v>
+      </c>
+      <c r="B35" t="s" s="2">
+        <v>294</v>
+      </c>
+      <c r="C35" s="2"/>
+      <c r="D35" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E35" s="2"/>
+      <c r="F35" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G35" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H35" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="I35" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J35" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="K35" t="s" s="2">
+        <v>223</v>
+      </c>
+      <c r="L35" t="s" s="2">
+        <v>264</v>
+      </c>
+      <c r="M35" t="s" s="2">
+        <v>265</v>
+      </c>
+      <c r="N35" t="s" s="2">
+        <v>266</v>
+      </c>
+      <c r="O35" t="s" s="2">
+        <v>267</v>
+      </c>
+      <c r="P35" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q35" s="2"/>
+      <c r="R35" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S35" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T35" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U35" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V35" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W35" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X35" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y35" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z35" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA35" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB35" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC35" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD35" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE35" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF35" t="s" s="2">
+        <v>268</v>
+      </c>
+      <c r="AG35" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH35" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI35" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ35" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK35" t="s" s="2">
+        <v>269</v>
+      </c>
+      <c r="AL35" t="s" s="2">
+        <v>270</v>
+      </c>
+      <c r="AM35" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN35" t="s" s="2">
         <v>77</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AN27">
+  <autoFilter ref="A1:AN35">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -4322,7 +5318,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI26">
+  <conditionalFormatting sqref="A2:AI34">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/dev/StructureDefinition-ph-core-practitioner.xlsx
+++ b/dev/StructureDefinition-ph-core-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-10T05:32:03+00:00</t>
+    <t>2026-04-10T05:44:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/StructureDefinition-ph-core-practitioner.xlsx
+++ b/dev/StructureDefinition-ph-core-practitioner.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$35</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$47</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1305" uniqueCount="295">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1735" uniqueCount="372">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-10T05:44:36+00:00</t>
+    <t>2026-05-26T03:51:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -428,33 +428,88 @@
     <t>Practitioner.extension</t>
   </si>
   <si>
+    <t xml:space="preserve">Extension
+</t>
+  </si>
+  <si>
+    <t>Extension</t>
+  </si>
+  <si>
+    <t>An Extension</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value:url}
+</t>
+  </si>
+  <si>
+    <t>open</t>
+  </si>
+  <si>
+    <t>DomainResource.extension</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
+  </si>
+  <si>
+    <t>Practitioner.extension:genderIdentity</t>
+  </si>
+  <si>
+    <t>genderIdentity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {individual-genderIdentity}
+</t>
+  </si>
+  <si>
+    <t>Gender Identity - in compliance with SOGIE Bill</t>
+  </si>
+  <si>
+    <t>An individual's personal sense of being a man, woman, boy, girl, nonbinary, or something else.</t>
+  </si>
+  <si>
+    <t>This represents an individual’s identity, ascertained by asking them what that identity is.</t>
+  </si>
+  <si>
+    <t>Practitioner.extension:individualPronouns</t>
+  </si>
+  <si>
+    <t>individualPronouns</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {individual-pronouns}
+</t>
+  </si>
+  <si>
+    <t>Individual pronouns - in compliance with SOGIE Bill</t>
+  </si>
+  <si>
+    <t>The pronouns to use when referring to an individual in verbal or written communication.</t>
+  </si>
+  <si>
+    <t>Practitioner.extension:sex</t>
+  </si>
+  <si>
+    <t>sex</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {individual-recordedSexOrGender}
+</t>
+  </si>
+  <si>
+    <t>Sex assigned at birth - in compliance with SOGIE Bill</t>
+  </si>
+  <si>
+    <t>A sex or gender property for the individual from a document or other record</t>
+  </si>
+  <si>
+    <t>Practitioner.modifierExtension</t>
+  </si>
+  <si>
     <t>extensions
 user content</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension
-</t>
-  </si>
-  <si>
-    <t>Additional content defined by implementations</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the resource. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
-  </si>
-  <si>
-    <t>DomainResource.extension</t>
-  </si>
-  <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
-  </si>
-  <si>
-    <t>Practitioner.modifierExtension</t>
-  </si>
-  <si>
     <t>Extensions that cannot be ignored</t>
   </si>
   <si>
@@ -462,6 +517,9 @@
 Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
   </si>
   <si>
+    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
+  </si>
+  <si>
     <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4/extensibility.html#modifierExtension).</t>
   </si>
   <si>
@@ -527,7 +585,7 @@
     <t>Practitioner.name</t>
   </si>
   <si>
-    <t xml:space="preserve">HumanName
+    <t xml:space="preserve">HumanName {http://doh.gov.ph/fhir/ph-core/StructureDefinition/ph-core-name}
 </t>
   </si>
   <si>
@@ -560,6 +618,223 @@
     <t>./PreferredName (GivenNames, FamilyName, TitleCode)</t>
   </si>
   <si>
+    <t>Practitioner.name.id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">string
+</t>
+  </si>
+  <si>
+    <t>Unique id for inter-element referencing</t>
+  </si>
+  <si>
+    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
+  </si>
+  <si>
+    <t>Element.id</t>
+  </si>
+  <si>
+    <t>n/a</t>
+  </si>
+  <si>
+    <t>Practitioner.name.extension</t>
+  </si>
+  <si>
+    <t>Additional content defined by implementations</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+  </si>
+  <si>
+    <t>Extensions are always sliced by (at least) url</t>
+  </si>
+  <si>
+    <t>Element.extension</t>
+  </si>
+  <si>
+    <t>Practitioner.name.use</t>
+  </si>
+  <si>
+    <t>usual | official | temp | nickname | anonymous | old | maiden</t>
+  </si>
+  <si>
+    <t>Identifies the purpose for this name.</t>
+  </si>
+  <si>
+    <t>Applications can assume that a name is current unless it explicitly says that it is temporary or old.</t>
+  </si>
+  <si>
+    <t>Allows the appropriate name for a particular context of use to be selected from among a set of names.</t>
+  </si>
+  <si>
+    <t>required</t>
+  </si>
+  <si>
+    <t>The use of a human name.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/name-use|4.0.1</t>
+  </si>
+  <si>
+    <t>HumanName.use</t>
+  </si>
+  <si>
+    <t>XPN.7, but often indicated by which field contains the name</t>
+  </si>
+  <si>
+    <t>unique(./use)</t>
+  </si>
+  <si>
+    <t>./NamePurpose</t>
+  </si>
+  <si>
+    <t>Practitioner.name.text</t>
+  </si>
+  <si>
+    <t>Text representation of the full name</t>
+  </si>
+  <si>
+    <t>Specifies the entire name as it should be displayed e.g. on an application UI. This may be provided instead of or as well as the specific parts.</t>
+  </si>
+  <si>
+    <t>Can provide both a text representation and parts. Applications updating a name SHALL ensure that when both text and parts are present,  no content is included in the text that isn't found in a part.</t>
+  </si>
+  <si>
+    <t>A renderable, unencoded form.</t>
+  </si>
+  <si>
+    <t>HumanName.text</t>
+  </si>
+  <si>
+    <t>implied by XPN.11</t>
+  </si>
+  <si>
+    <t>./formatted</t>
+  </si>
+  <si>
+    <t>Practitioner.name.family</t>
+  </si>
+  <si>
+    <t xml:space="preserve">surname
+</t>
+  </si>
+  <si>
+    <t>Family name (often called 'Surname')</t>
+  </si>
+  <si>
+    <t>The part of a name that links to the genealogy. In some cultures (e.g. Eritrea) the family name of a son is the first name of his father.</t>
+  </si>
+  <si>
+    <t>Family Name may be decomposed into specific parts using extensions (de, nl, es related cultures).</t>
+  </si>
+  <si>
+    <t>HumanName.family</t>
+  </si>
+  <si>
+    <t>XPN.1/FN.1</t>
+  </si>
+  <si>
+    <t>./part[partType = FAM]</t>
+  </si>
+  <si>
+    <t>./FamilyName</t>
+  </si>
+  <si>
+    <t>Practitioner.name.given</t>
+  </si>
+  <si>
+    <t>first name
+middle name</t>
+  </si>
+  <si>
+    <t>First and middle names</t>
+  </si>
+  <si>
+    <t>First name (given[0]) and Middle Name (given[1]).</t>
+  </si>
+  <si>
+    <t>If only initials are recorded, they may be used in place of the full name parts. Initials may be separated into multiple given names but often aren't due to paractical limitations.  This element is not called "first name" since given names do not always come first.</t>
+  </si>
+  <si>
+    <t>HumanName.given</t>
+  </si>
+  <si>
+    <t>XPN.2 + XPN.3</t>
+  </si>
+  <si>
+    <t>./part[partType = GIV]</t>
+  </si>
+  <si>
+    <t>./GivenNames</t>
+  </si>
+  <si>
+    <t>Practitioner.name.prefix</t>
+  </si>
+  <si>
+    <t>Parts that come before the name</t>
+  </si>
+  <si>
+    <t>Part of the name that is acquired as a title due to academic, legal, employment or nobility status, etc. and that appears at the start of the name.</t>
+  </si>
+  <si>
+    <t>HumanName.prefix</t>
+  </si>
+  <si>
+    <t>XPN.5</t>
+  </si>
+  <si>
+    <t>./part[partType = PFX]</t>
+  </si>
+  <si>
+    <t>./TitleCode</t>
+  </si>
+  <si>
+    <t>Practitioner.name.suffix</t>
+  </si>
+  <si>
+    <t>Parts that come after the name</t>
+  </si>
+  <si>
+    <t>Part of the name that is acquired as a title due to academic, legal, employment or nobility status, etc. and that appears at the end of the name.</t>
+  </si>
+  <si>
+    <t>HumanName.suffix</t>
+  </si>
+  <si>
+    <t>XPN/4</t>
+  </si>
+  <si>
+    <t>./part[partType = SFX]</t>
+  </si>
+  <si>
+    <t>Practitioner.name.period</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Period
+</t>
+  </si>
+  <si>
+    <t>Time period when name was/is in use</t>
+  </si>
+  <si>
+    <t>Indicates the period of time when this name was valid for the named person.</t>
+  </si>
+  <si>
+    <t>Allows names to be placed in historical context.</t>
+  </si>
+  <si>
+    <t>HumanName.period</t>
+  </si>
+  <si>
+    <t>XPN.13 + XPN.14</t>
+  </si>
+  <si>
+    <t>./usablePeriod[type="IVL&lt;TS&gt;"]</t>
+  </si>
+  <si>
+    <t>./StartDate and ./EndDate</t>
+  </si>
+  <si>
     <t>Practitioner.telecom</t>
   </si>
   <si>
@@ -629,9 +904,6 @@
     <t>Needed to address the person correctly.</t>
   </si>
   <si>
-    <t>required</t>
-  </si>
-  <si>
     <t>The gender of a person used for administrative purposes.</t>
   </si>
   <si>
@@ -719,29 +991,7 @@
     <t>Practitioner.qualification.id</t>
   </si>
   <si>
-    <t xml:space="preserve">string
-</t>
-  </si>
-  <si>
-    <t>Unique id for inter-element referencing</t>
-  </si>
-  <si>
-    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
-  </si>
-  <si>
-    <t>Element.id</t>
-  </si>
-  <si>
-    <t>n/a</t>
-  </si>
-  <si>
     <t>Practitioner.qualification.extension</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t>Element.extension</t>
   </si>
   <si>
     <t>Practitioner.qualification.modifierExtension</t>
@@ -807,16 +1057,6 @@
     <t>Practitioner.qualification.code.extension</t>
   </si>
   <si>
-    <t xml:space="preserve">value:url}
-</t>
-  </si>
-  <si>
-    <t>Extensions are always sliced by (at least) url</t>
-  </si>
-  <si>
-    <t>open</t>
-  </si>
-  <si>
     <t>Practitioner.qualification.code.coding</t>
   </si>
   <si>
@@ -870,10 +1110,6 @@
   </si>
   <si>
     <t>Practitioner.qualification.period</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Period
-</t>
   </si>
   <si>
     <t>Period during which the qualification is valid</t>
@@ -1257,12 +1493,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AN35"/>
+  <dimension ref="A1:AN47"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="34.8984375" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="34.8984375" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="10.8515625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="3" max="3" width="15.84765625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
@@ -1270,7 +1506,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="61.85546875" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="64.0859375" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1295,7 +1531,7 @@
     <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="39.109375" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="48.16015625" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="47.515625" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="44.90625" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="31.65234375" customWidth="true" bestFit="true"/>
@@ -2226,7 +2462,7 @@
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
-        <v>133</v>
+        <v>77</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
@@ -2245,17 +2481,15 @@
         <v>77</v>
       </c>
       <c r="K9" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="L9" t="s" s="2">
         <v>134</v>
       </c>
-      <c r="L9" t="s" s="2">
+      <c r="M9" t="s" s="2">
         <v>135</v>
       </c>
-      <c r="M9" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="N9" t="s" s="2">
-        <v>137</v>
-      </c>
+      <c r="N9" s="2"/>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
         <v>77</v>
@@ -2292,16 +2526,14 @@
         <v>77</v>
       </c>
       <c r="AB9" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC9" t="s" s="2">
-        <v>77</v>
-      </c>
+        <v>136</v>
+      </c>
+      <c r="AC9" s="2"/>
       <c r="AD9" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE9" t="s" s="2">
-        <v>77</v>
+        <v>137</v>
       </c>
       <c r="AF9" t="s" s="2">
         <v>138</v>
@@ -2322,7 +2554,7 @@
         <v>77</v>
       </c>
       <c r="AL9" t="s" s="2">
-        <v>131</v>
+        <v>77</v>
       </c>
       <c r="AM9" t="s" s="2">
         <v>77</v>
@@ -2336,11 +2568,13 @@
         <v>140</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="C10" s="2"/>
+        <v>132</v>
+      </c>
+      <c r="C10" t="s" s="2">
+        <v>141</v>
+      </c>
       <c r="D10" t="s" s="2">
-        <v>133</v>
+        <v>77</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
@@ -2353,26 +2587,24 @@
         <v>77</v>
       </c>
       <c r="I10" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="J10" t="s" s="2">
         <v>77</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>134</v>
+        <v>142</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="N10" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="O10" t="s" s="2">
-        <v>143</v>
-      </c>
+        <v>145</v>
+      </c>
+      <c r="O10" s="2"/>
       <c r="P10" t="s" s="2">
         <v>77</v>
       </c>
@@ -2420,7 +2652,7 @@
         <v>77</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>78</v>
@@ -2438,7 +2670,7 @@
         <v>77</v>
       </c>
       <c r="AL10" t="s" s="2">
-        <v>131</v>
+        <v>77</v>
       </c>
       <c r="AM10" t="s" s="2">
         <v>77</v>
@@ -2449,12 +2681,14 @@
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>145</v>
-      </c>
-      <c r="C11" s="2"/>
+        <v>132</v>
+      </c>
+      <c r="C11" t="s" s="2">
+        <v>147</v>
+      </c>
       <c r="D11" t="s" s="2">
         <v>77</v>
       </c>
@@ -2472,21 +2706,19 @@
         <v>77</v>
       </c>
       <c r="J11" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="N11" s="2"/>
-      <c r="O11" t="s" s="2">
-        <v>149</v>
-      </c>
+      <c r="O11" s="2"/>
       <c r="P11" t="s" s="2">
         <v>77</v>
       </c>
@@ -2534,7 +2766,7 @@
         <v>77</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>145</v>
+        <v>138</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>78</v>
@@ -2546,29 +2778,31 @@
         <v>77</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="AK11" t="s" s="2">
-        <v>150</v>
+        <v>77</v>
       </c>
       <c r="AL11" t="s" s="2">
-        <v>151</v>
+        <v>77</v>
       </c>
       <c r="AM11" t="s" s="2">
-        <v>152</v>
+        <v>77</v>
       </c>
       <c r="AN11" t="s" s="2">
-        <v>153</v>
+        <v>77</v>
       </c>
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>154</v>
-      </c>
-      <c r="C12" s="2"/>
+        <v>132</v>
+      </c>
+      <c r="C12" t="s" s="2">
+        <v>152</v>
+      </c>
       <c r="D12" t="s" s="2">
         <v>77</v>
       </c>
@@ -2577,7 +2811,7 @@
         <v>78</v>
       </c>
       <c r="G12" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H12" t="s" s="2">
         <v>77</v>
@@ -2586,29 +2820,23 @@
         <v>77</v>
       </c>
       <c r="J12" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="K12" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="L12" t="s" s="2">
+        <v>154</v>
+      </c>
+      <c r="M12" t="s" s="2">
         <v>155</v>
       </c>
-      <c r="L12" t="s" s="2">
-        <v>156</v>
-      </c>
-      <c r="M12" t="s" s="2">
-        <v>157</v>
-      </c>
-      <c r="N12" t="s" s="2">
-        <v>158</v>
-      </c>
-      <c r="O12" t="s" s="2">
-        <v>159</v>
-      </c>
+      <c r="N12" s="2"/>
+      <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
         <v>77</v>
       </c>
-      <c r="Q12" t="s" s="2">
-        <v>160</v>
-      </c>
+      <c r="Q12" s="2"/>
       <c r="R12" t="s" s="2">
         <v>77</v>
       </c>
@@ -2652,43 +2880,43 @@
         <v>77</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>154</v>
+        <v>138</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH12" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI12" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="AK12" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL12" t="s" s="2">
-        <v>161</v>
+        <v>77</v>
       </c>
       <c r="AM12" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN12" t="s" s="2">
-        <v>162</v>
+        <v>77</v>
       </c>
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
-        <v>77</v>
+        <v>157</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
@@ -2701,25 +2929,25 @@
         <v>77</v>
       </c>
       <c r="I13" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="J13" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>164</v>
+        <v>133</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="O13" t="s" s="2">
-        <v>168</v>
+        <v>161</v>
       </c>
       <c r="P13" t="s" s="2">
         <v>77</v>
@@ -2768,7 +2996,7 @@
         <v>77</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>78</v>
@@ -2780,16 +3008,16 @@
         <v>77</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>169</v>
+        <v>77</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>170</v>
+        <v>131</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>171</v>
+        <v>77</v>
       </c>
       <c r="AN13" t="s" s="2">
         <v>77</v>
@@ -2797,10 +3025,10 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>172</v>
+        <v>163</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>172</v>
+        <v>163</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -2823,19 +3051,17 @@
         <v>89</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>173</v>
+        <v>164</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>174</v>
+        <v>165</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>175</v>
-      </c>
-      <c r="N14" t="s" s="2">
-        <v>176</v>
-      </c>
+        <v>166</v>
+      </c>
+      <c r="N14" s="2"/>
       <c r="O14" t="s" s="2">
-        <v>177</v>
+        <v>167</v>
       </c>
       <c r="P14" t="s" s="2">
         <v>77</v>
@@ -2884,7 +3110,7 @@
         <v>77</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>172</v>
+        <v>163</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>78</v>
@@ -2899,24 +3125,24 @@
         <v>100</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>178</v>
+        <v>168</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>179</v>
+        <v>169</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="AN14" t="s" s="2">
-        <v>77</v>
+        <v>171</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>181</v>
+        <v>172</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>181</v>
+        <v>172</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -2927,10 +3153,10 @@
         <v>78</v>
       </c>
       <c r="G15" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H15" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="I15" t="s" s="2">
         <v>77</v>
@@ -2939,24 +3165,26 @@
         <v>89</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>183</v>
+        <v>174</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>184</v>
+        <v>175</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="O15" t="s" s="2">
-        <v>186</v>
+        <v>177</v>
       </c>
       <c r="P15" t="s" s="2">
         <v>77</v>
       </c>
-      <c r="Q15" s="2"/>
+      <c r="Q15" t="s" s="2">
+        <v>178</v>
+      </c>
       <c r="R15" t="s" s="2">
         <v>77</v>
       </c>
@@ -3000,13 +3228,13 @@
         <v>77</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>181</v>
+        <v>172</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH15" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI15" t="s" s="2">
         <v>77</v>
@@ -3015,24 +3243,24 @@
         <v>100</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>187</v>
+        <v>77</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>188</v>
+        <v>179</v>
       </c>
       <c r="AM15" t="s" s="2">
-        <v>189</v>
+        <v>77</v>
       </c>
       <c r="AN15" t="s" s="2">
-        <v>77</v>
+        <v>180</v>
       </c>
     </row>
-    <row r="16" hidden="true">
+    <row r="16">
       <c r="A16" t="s" s="2">
-        <v>190</v>
+        <v>181</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>190</v>
+        <v>181</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -3043,10 +3271,10 @@
         <v>78</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H16" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="I16" t="s" s="2">
         <v>77</v>
@@ -3055,17 +3283,19 @@
         <v>89</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>108</v>
+        <v>182</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>191</v>
+        <v>183</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>192</v>
-      </c>
-      <c r="N16" s="2"/>
+        <v>184</v>
+      </c>
+      <c r="N16" t="s" s="2">
+        <v>185</v>
+      </c>
       <c r="O16" t="s" s="2">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="P16" t="s" s="2">
         <v>77</v>
@@ -3090,13 +3320,13 @@
         <v>77</v>
       </c>
       <c r="X16" t="s" s="2">
-        <v>194</v>
+        <v>77</v>
       </c>
       <c r="Y16" t="s" s="2">
-        <v>195</v>
+        <v>77</v>
       </c>
       <c r="Z16" t="s" s="2">
-        <v>196</v>
+        <v>77</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>77</v>
@@ -3114,13 +3344,13 @@
         <v>77</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>190</v>
+        <v>181</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH16" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI16" t="s" s="2">
         <v>77</v>
@@ -3129,13 +3359,13 @@
         <v>100</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>197</v>
+        <v>187</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>198</v>
+        <v>188</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>199</v>
+        <v>189</v>
       </c>
       <c r="AN16" t="s" s="2">
         <v>77</v>
@@ -3143,10 +3373,10 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3166,21 +3396,19 @@
         <v>77</v>
       </c>
       <c r="J17" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>201</v>
+        <v>191</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>202</v>
+        <v>192</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>203</v>
+        <v>193</v>
       </c>
       <c r="N17" s="2"/>
-      <c r="O17" t="s" s="2">
-        <v>204</v>
-      </c>
+      <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
         <v>77</v>
       </c>
@@ -3228,7 +3456,7 @@
         <v>77</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>200</v>
+        <v>194</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>78</v>
@@ -3240,16 +3468,16 @@
         <v>77</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>100</v>
+        <v>77</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>205</v>
+        <v>77</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>206</v>
+        <v>195</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>207</v>
+        <v>77</v>
       </c>
       <c r="AN17" t="s" s="2">
         <v>77</v>
@@ -3257,14 +3485,14 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>208</v>
+        <v>196</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>208</v>
+        <v>196</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
-        <v>77</v>
+        <v>157</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
@@ -3283,18 +3511,18 @@
         <v>77</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>209</v>
+        <v>133</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>210</v>
+        <v>197</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>211</v>
-      </c>
-      <c r="N18" s="2"/>
-      <c r="O18" t="s" s="2">
-        <v>212</v>
-      </c>
+        <v>198</v>
+      </c>
+      <c r="N18" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
         <v>77</v>
       </c>
@@ -3330,19 +3558,19 @@
         <v>77</v>
       </c>
       <c r="AB18" t="s" s="2">
-        <v>77</v>
+        <v>136</v>
       </c>
       <c r="AC18" t="s" s="2">
-        <v>77</v>
+        <v>199</v>
       </c>
       <c r="AD18" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE18" t="s" s="2">
-        <v>77</v>
+        <v>137</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>208</v>
+        <v>200</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>78</v>
@@ -3354,16 +3582,16 @@
         <v>77</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="AK18" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>213</v>
+        <v>195</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>214</v>
+        <v>77</v>
       </c>
       <c r="AN18" t="s" s="2">
         <v>77</v>
@@ -3371,10 +3599,10 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>215</v>
+        <v>201</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>215</v>
+        <v>201</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3385,28 +3613,32 @@
         <v>78</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H19" t="s" s="2">
         <v>77</v>
       </c>
       <c r="I19" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="J19" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>216</v>
+        <v>108</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>217</v>
+        <v>202</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>218</v>
-      </c>
-      <c r="N19" s="2"/>
-      <c r="O19" s="2"/>
+        <v>203</v>
+      </c>
+      <c r="N19" t="s" s="2">
+        <v>204</v>
+      </c>
+      <c r="O19" t="s" s="2">
+        <v>205</v>
+      </c>
       <c r="P19" t="s" s="2">
         <v>77</v>
       </c>
@@ -3430,13 +3662,13 @@
         <v>77</v>
       </c>
       <c r="X19" t="s" s="2">
-        <v>77</v>
+        <v>206</v>
       </c>
       <c r="Y19" t="s" s="2">
-        <v>77</v>
+        <v>207</v>
       </c>
       <c r="Z19" t="s" s="2">
-        <v>77</v>
+        <v>208</v>
       </c>
       <c r="AA19" t="s" s="2">
         <v>77</v>
@@ -3454,13 +3686,13 @@
         <v>77</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>215</v>
+        <v>209</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH19" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI19" t="s" s="2">
         <v>77</v>
@@ -3469,13 +3701,13 @@
         <v>100</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>219</v>
+        <v>210</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>220</v>
+        <v>211</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>221</v>
+        <v>212</v>
       </c>
       <c r="AN19" t="s" s="2">
         <v>77</v>
@@ -3483,10 +3715,10 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>222</v>
+        <v>213</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>222</v>
+        <v>213</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3506,19 +3738,23 @@
         <v>77</v>
       </c>
       <c r="J20" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>223</v>
+        <v>191</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>224</v>
+        <v>214</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>225</v>
-      </c>
-      <c r="N20" s="2"/>
-      <c r="O20" s="2"/>
+        <v>215</v>
+      </c>
+      <c r="N20" t="s" s="2">
+        <v>216</v>
+      </c>
+      <c r="O20" t="s" s="2">
+        <v>217</v>
+      </c>
       <c r="P20" t="s" s="2">
         <v>77</v>
       </c>
@@ -3566,7 +3802,7 @@
         <v>77</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>226</v>
+        <v>218</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>78</v>
@@ -3578,13 +3814,13 @@
         <v>77</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>77</v>
+        <v>219</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>227</v>
+        <v>220</v>
       </c>
       <c r="AM20" t="s" s="2">
         <v>77</v>
@@ -3593,44 +3829,44 @@
         <v>77</v>
       </c>
     </row>
-    <row r="21" hidden="true">
+    <row r="21">
       <c r="A21" t="s" s="2">
-        <v>228</v>
+        <v>221</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>228</v>
+        <v>221</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>133</v>
+        <v>222</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H21" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="I21" t="s" s="2">
         <v>77</v>
       </c>
       <c r="J21" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>134</v>
+        <v>191</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>135</v>
+        <v>223</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>137</v>
+        <v>225</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
@@ -3680,43 +3916,43 @@
         <v>77</v>
       </c>
       <c r="AF21" t="s" s="2">
+        <v>226</v>
+      </c>
+      <c r="AG21" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH21" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI21" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ21" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK21" t="s" s="2">
+        <v>227</v>
+      </c>
+      <c r="AL21" t="s" s="2">
+        <v>228</v>
+      </c>
+      <c r="AM21" t="s" s="2">
+        <v>229</v>
+      </c>
+      <c r="AN21" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s" s="2">
         <v>230</v>
       </c>
-      <c r="AG21" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH21" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI21" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ21" t="s" s="2">
-        <v>139</v>
-      </c>
-      <c r="AK21" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AL21" t="s" s="2">
-        <v>227</v>
-      </c>
-      <c r="AM21" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN21" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="22" hidden="true">
-      <c r="A22" t="s" s="2">
-        <v>231</v>
-      </c>
       <c r="B22" t="s" s="2">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
@@ -3726,29 +3962,27 @@
         <v>79</v>
       </c>
       <c r="H22" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="I22" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="J22" t="s" s="2">
         <v>89</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>134</v>
+        <v>191</v>
       </c>
       <c r="L22" t="s" s="2">
+        <v>232</v>
+      </c>
+      <c r="M22" t="s" s="2">
         <v>233</v>
       </c>
-      <c r="M22" t="s" s="2">
+      <c r="N22" t="s" s="2">
         <v>234</v>
       </c>
-      <c r="N22" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="O22" t="s" s="2">
-        <v>143</v>
-      </c>
+      <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
         <v>77</v>
       </c>
@@ -3808,16 +4042,16 @@
         <v>77</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>139</v>
+        <v>100</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>77</v>
+        <v>236</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>131</v>
+        <v>237</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>77</v>
+        <v>238</v>
       </c>
       <c r="AN22" t="s" s="2">
         <v>77</v>
@@ -3825,10 +4059,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3848,21 +4082,19 @@
         <v>77</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>146</v>
+        <v>191</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="N23" s="2"/>
-      <c r="O23" t="s" s="2">
-        <v>239</v>
-      </c>
+      <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
         <v>77</v>
       </c>
@@ -3910,7 +4142,7 @@
         <v>77</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>78</v>
@@ -3925,24 +4157,24 @@
         <v>100</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>77</v>
+        <v>243</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>77</v>
+        <v>245</v>
       </c>
       <c r="AN23" t="s" s="2">
         <v>77</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>241</v>
+        <v>246</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>241</v>
+        <v>246</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -3950,28 +4182,28 @@
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H24" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I24" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J24" t="s" s="2">
         <v>89</v>
       </c>
-      <c r="I24" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J24" t="s" s="2">
-        <v>77</v>
-      </c>
       <c r="K24" t="s" s="2">
-        <v>242</v>
+        <v>191</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -3998,13 +4230,13 @@
         <v>77</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>245</v>
+        <v>77</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>246</v>
+        <v>77</v>
       </c>
       <c r="Z24" t="s" s="2">
-        <v>247</v>
+        <v>77</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>77</v>
@@ -4022,13 +4254,13 @@
         <v>77</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>241</v>
+        <v>249</v>
       </c>
       <c r="AG24" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI24" t="s" s="2">
         <v>77</v>
@@ -4037,13 +4269,13 @@
         <v>100</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>77</v>
+        <v>250</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>220</v>
+        <v>251</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>248</v>
+        <v>77</v>
       </c>
       <c r="AN24" t="s" s="2">
         <v>77</v>
@@ -4051,10 +4283,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4074,19 +4306,21 @@
         <v>77</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>223</v>
+        <v>253</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>224</v>
+        <v>254</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>225</v>
+        <v>255</v>
       </c>
       <c r="N25" s="2"/>
-      <c r="O25" s="2"/>
+      <c r="O25" t="s" s="2">
+        <v>256</v>
+      </c>
       <c r="P25" t="s" s="2">
         <v>77</v>
       </c>
@@ -4134,7 +4368,7 @@
         <v>77</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>226</v>
+        <v>257</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>78</v>
@@ -4146,31 +4380,31 @@
         <v>77</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>77</v>
+        <v>258</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>227</v>
+        <v>259</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>77</v>
+        <v>260</v>
       </c>
       <c r="AN25" t="s" s="2">
         <v>77</v>
       </c>
     </row>
-    <row r="26" hidden="true">
+    <row r="26">
       <c r="A26" t="s" s="2">
-        <v>250</v>
+        <v>261</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>250</v>
+        <v>261</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>133</v>
+        <v>77</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
@@ -4180,27 +4414,29 @@
         <v>79</v>
       </c>
       <c r="H26" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="I26" t="s" s="2">
         <v>77</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>134</v>
+        <v>262</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>135</v>
+        <v>263</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>229</v>
+        <v>264</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="O26" s="2"/>
+        <v>265</v>
+      </c>
+      <c r="O26" t="s" s="2">
+        <v>266</v>
+      </c>
       <c r="P26" t="s" s="2">
         <v>77</v>
       </c>
@@ -4236,19 +4472,19 @@
         <v>77</v>
       </c>
       <c r="AB26" t="s" s="2">
-        <v>251</v>
+        <v>77</v>
       </c>
       <c r="AC26" t="s" s="2">
-        <v>252</v>
+        <v>77</v>
       </c>
       <c r="AD26" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE26" t="s" s="2">
-        <v>253</v>
+        <v>77</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>230</v>
+        <v>261</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>78</v>
@@ -4260,16 +4496,16 @@
         <v>77</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>139</v>
+        <v>100</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>77</v>
+        <v>267</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>227</v>
+        <v>268</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>77</v>
+        <v>269</v>
       </c>
       <c r="AN26" t="s" s="2">
         <v>77</v>
@@ -4277,10 +4513,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>254</v>
+        <v>270</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>254</v>
+        <v>270</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4303,19 +4539,19 @@
         <v>89</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>255</v>
+        <v>271</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>256</v>
+        <v>272</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>257</v>
+        <v>273</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>258</v>
+        <v>274</v>
       </c>
       <c r="O27" t="s" s="2">
-        <v>259</v>
+        <v>275</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>77</v>
@@ -4364,7 +4600,7 @@
         <v>77</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>260</v>
+        <v>270</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>78</v>
@@ -4379,13 +4615,13 @@
         <v>100</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>261</v>
+        <v>276</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>262</v>
+        <v>277</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>77</v>
+        <v>278</v>
       </c>
       <c r="AN27" t="s" s="2">
         <v>77</v>
@@ -4393,10 +4629,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>263</v>
+        <v>279</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>263</v>
+        <v>279</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4419,19 +4655,17 @@
         <v>89</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>223</v>
+        <v>108</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>264</v>
+        <v>280</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>265</v>
-      </c>
-      <c r="N28" t="s" s="2">
-        <v>266</v>
-      </c>
+        <v>281</v>
+      </c>
+      <c r="N28" s="2"/>
       <c r="O28" t="s" s="2">
-        <v>267</v>
+        <v>282</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>77</v>
@@ -4456,13 +4690,13 @@
         <v>77</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>77</v>
+        <v>206</v>
       </c>
       <c r="Y28" t="s" s="2">
-        <v>77</v>
+        <v>283</v>
       </c>
       <c r="Z28" t="s" s="2">
-        <v>77</v>
+        <v>284</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>77</v>
@@ -4480,7 +4714,7 @@
         <v>77</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>268</v>
+        <v>279</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>78</v>
@@ -4495,24 +4729,24 @@
         <v>100</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>269</v>
+        <v>285</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>270</v>
+        <v>286</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>77</v>
+        <v>287</v>
       </c>
       <c r="AN28" t="s" s="2">
         <v>77</v>
       </c>
     </row>
-    <row r="29" hidden="true">
+    <row r="29">
       <c r="A29" t="s" s="2">
-        <v>271</v>
+        <v>288</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>271</v>
+        <v>288</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4526,26 +4760,26 @@
         <v>88</v>
       </c>
       <c r="H29" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="I29" t="s" s="2">
         <v>77</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>272</v>
+        <v>289</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>273</v>
+        <v>290</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>274</v>
+        <v>291</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" t="s" s="2">
-        <v>275</v>
+        <v>292</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>77</v>
@@ -4594,7 +4828,7 @@
         <v>77</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>271</v>
+        <v>288</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>78</v>
@@ -4609,13 +4843,13 @@
         <v>100</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>77</v>
+        <v>293</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>276</v>
+        <v>294</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>277</v>
+        <v>295</v>
       </c>
       <c r="AN29" t="s" s="2">
         <v>77</v>
@@ -4623,10 +4857,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>278</v>
+        <v>296</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>278</v>
+        <v>296</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4637,7 +4871,7 @@
         <v>78</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>77</v>
@@ -4649,16 +4883,18 @@
         <v>77</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>279</v>
+        <v>297</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>280</v>
+        <v>298</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>281</v>
+        <v>299</v>
       </c>
       <c r="N30" s="2"/>
-      <c r="O30" s="2"/>
+      <c r="O30" t="s" s="2">
+        <v>300</v>
+      </c>
       <c r="P30" t="s" s="2">
         <v>77</v>
       </c>
@@ -4706,13 +4942,13 @@
         <v>77</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>278</v>
+        <v>296</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>77</v>
@@ -4724,21 +4960,21 @@
         <v>77</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>282</v>
+        <v>301</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>77</v>
+        <v>302</v>
       </c>
       <c r="AN30" t="s" s="2">
         <v>77</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>283</v>
+        <v>303</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>283</v>
+        <v>303</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -4752,7 +4988,7 @@
         <v>79</v>
       </c>
       <c r="H31" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="I31" t="s" s="2">
         <v>77</v>
@@ -4761,20 +4997,16 @@
         <v>77</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>242</v>
+        <v>304</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>284</v>
+        <v>305</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>285</v>
-      </c>
-      <c r="N31" t="s" s="2">
-        <v>286</v>
-      </c>
-      <c r="O31" t="s" s="2">
-        <v>287</v>
-      </c>
+        <v>306</v>
+      </c>
+      <c r="N31" s="2"/>
+      <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
         <v>77</v>
       </c>
@@ -4798,13 +5030,13 @@
         <v>77</v>
       </c>
       <c r="X31" t="s" s="2">
-        <v>112</v>
+        <v>77</v>
       </c>
       <c r="Y31" t="s" s="2">
-        <v>113</v>
+        <v>77</v>
       </c>
       <c r="Z31" t="s" s="2">
-        <v>114</v>
+        <v>77</v>
       </c>
       <c r="AA31" t="s" s="2">
         <v>77</v>
@@ -4822,7 +5054,7 @@
         <v>77</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>283</v>
+        <v>303</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>78</v>
@@ -4837,13 +5069,13 @@
         <v>100</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>288</v>
+        <v>307</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>289</v>
+        <v>308</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>290</v>
+        <v>309</v>
       </c>
       <c r="AN31" t="s" s="2">
         <v>77</v>
@@ -4851,10 +5083,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>291</v>
+        <v>310</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>291</v>
+        <v>310</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -4877,13 +5109,13 @@
         <v>77</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>223</v>
+        <v>191</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>224</v>
+        <v>192</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>225</v>
+        <v>193</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -4934,7 +5166,7 @@
         <v>77</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>226</v>
+        <v>194</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>78</v>
@@ -4952,7 +5184,7 @@
         <v>77</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>227</v>
+        <v>195</v>
       </c>
       <c r="AM32" t="s" s="2">
         <v>77</v>
@@ -4963,14 +5195,14 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>292</v>
+        <v>311</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>292</v>
+        <v>311</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>133</v>
+        <v>157</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
@@ -4989,16 +5221,16 @@
         <v>77</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>135</v>
+        <v>197</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>229</v>
+        <v>198</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>137</v>
+        <v>160</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
@@ -5036,19 +5268,19 @@
         <v>77</v>
       </c>
       <c r="AB33" t="s" s="2">
-        <v>251</v>
+        <v>77</v>
       </c>
       <c r="AC33" t="s" s="2">
-        <v>252</v>
+        <v>77</v>
       </c>
       <c r="AD33" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE33" t="s" s="2">
-        <v>253</v>
+        <v>77</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>230</v>
+        <v>200</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>78</v>
@@ -5066,7 +5298,7 @@
         <v>77</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>227</v>
+        <v>195</v>
       </c>
       <c r="AM33" t="s" s="2">
         <v>77</v>
@@ -5075,16 +5307,16 @@
         <v>77</v>
       </c>
     </row>
-    <row r="34">
+    <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>293</v>
+        <v>312</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>293</v>
+        <v>312</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>77</v>
+        <v>313</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
@@ -5094,28 +5326,28 @@
         <v>79</v>
       </c>
       <c r="H34" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I34" t="s" s="2">
         <v>89</v>
-      </c>
-      <c r="I34" t="s" s="2">
-        <v>77</v>
       </c>
       <c r="J34" t="s" s="2">
         <v>89</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>255</v>
+        <v>133</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>256</v>
+        <v>314</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>257</v>
+        <v>315</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>258</v>
+        <v>160</v>
       </c>
       <c r="O34" t="s" s="2">
-        <v>259</v>
+        <v>161</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>77</v>
@@ -5164,7 +5396,7 @@
         <v>77</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>260</v>
+        <v>316</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>78</v>
@@ -5176,13 +5408,13 @@
         <v>77</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>261</v>
+        <v>77</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>262</v>
+        <v>131</v>
       </c>
       <c r="AM34" t="s" s="2">
         <v>77</v>
@@ -5191,12 +5423,12 @@
         <v>77</v>
       </c>
     </row>
-    <row r="35">
+    <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>294</v>
+        <v>317</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>294</v>
+        <v>317</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5207,31 +5439,29 @@
         <v>78</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H35" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="I35" t="s" s="2">
         <v>77</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>223</v>
+        <v>164</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>264</v>
+        <v>318</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>265</v>
-      </c>
-      <c r="N35" t="s" s="2">
-        <v>266</v>
-      </c>
+        <v>319</v>
+      </c>
+      <c r="N35" s="2"/>
       <c r="O35" t="s" s="2">
-        <v>267</v>
+        <v>320</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>77</v>
@@ -5280,13 +5510,13 @@
         <v>77</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>268</v>
+        <v>317</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI35" t="s" s="2">
         <v>77</v>
@@ -5295,20 +5525,1390 @@
         <v>100</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>269</v>
+        <v>77</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>270</v>
+        <v>321</v>
       </c>
       <c r="AM35" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN35" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="s" s="2">
+        <v>322</v>
+      </c>
+      <c r="B36" t="s" s="2">
+        <v>322</v>
+      </c>
+      <c r="C36" s="2"/>
+      <c r="D36" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E36" s="2"/>
+      <c r="F36" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="G36" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H36" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="I36" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J36" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K36" t="s" s="2">
+        <v>323</v>
+      </c>
+      <c r="L36" t="s" s="2">
+        <v>324</v>
+      </c>
+      <c r="M36" t="s" s="2">
+        <v>325</v>
+      </c>
+      <c r="N36" s="2"/>
+      <c r="O36" s="2"/>
+      <c r="P36" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q36" s="2"/>
+      <c r="R36" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S36" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T36" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U36" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V36" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W36" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X36" t="s" s="2">
+        <v>326</v>
+      </c>
+      <c r="Y36" t="s" s="2">
+        <v>327</v>
+      </c>
+      <c r="Z36" t="s" s="2">
+        <v>328</v>
+      </c>
+      <c r="AA36" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB36" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC36" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD36" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE36" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF36" t="s" s="2">
+        <v>322</v>
+      </c>
+      <c r="AG36" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AH36" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI36" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ36" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK36" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL36" t="s" s="2">
+        <v>308</v>
+      </c>
+      <c r="AM36" t="s" s="2">
+        <v>329</v>
+      </c>
+      <c r="AN36" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="37" hidden="true">
+      <c r="A37" t="s" s="2">
+        <v>330</v>
+      </c>
+      <c r="B37" t="s" s="2">
+        <v>330</v>
+      </c>
+      <c r="C37" s="2"/>
+      <c r="D37" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E37" s="2"/>
+      <c r="F37" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G37" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H37" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I37" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J37" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K37" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="L37" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="M37" t="s" s="2">
+        <v>193</v>
+      </c>
+      <c r="N37" s="2"/>
+      <c r="O37" s="2"/>
+      <c r="P37" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q37" s="2"/>
+      <c r="R37" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S37" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T37" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U37" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V37" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W37" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X37" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y37" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z37" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA37" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB37" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC37" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD37" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE37" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF37" t="s" s="2">
+        <v>194</v>
+      </c>
+      <c r="AG37" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH37" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI37" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ37" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AK37" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL37" t="s" s="2">
+        <v>195</v>
+      </c>
+      <c r="AM37" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN37" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="38" hidden="true">
+      <c r="A38" t="s" s="2">
+        <v>331</v>
+      </c>
+      <c r="B38" t="s" s="2">
+        <v>331</v>
+      </c>
+      <c r="C38" s="2"/>
+      <c r="D38" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="E38" s="2"/>
+      <c r="F38" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G38" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H38" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I38" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J38" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K38" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="L38" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="M38" t="s" s="2">
+        <v>198</v>
+      </c>
+      <c r="N38" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="O38" s="2"/>
+      <c r="P38" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q38" s="2"/>
+      <c r="R38" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S38" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T38" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U38" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V38" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W38" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X38" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y38" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z38" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA38" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB38" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="AC38" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="AD38" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE38" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="AF38" t="s" s="2">
+        <v>200</v>
+      </c>
+      <c r="AG38" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH38" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI38" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ38" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="AK38" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL38" t="s" s="2">
+        <v>195</v>
+      </c>
+      <c r="AM38" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN38" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="s" s="2">
+        <v>332</v>
+      </c>
+      <c r="B39" t="s" s="2">
+        <v>332</v>
+      </c>
+      <c r="C39" s="2"/>
+      <c r="D39" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E39" s="2"/>
+      <c r="F39" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G39" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H39" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="I39" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J39" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="K39" t="s" s="2">
+        <v>333</v>
+      </c>
+      <c r="L39" t="s" s="2">
+        <v>334</v>
+      </c>
+      <c r="M39" t="s" s="2">
+        <v>335</v>
+      </c>
+      <c r="N39" t="s" s="2">
+        <v>336</v>
+      </c>
+      <c r="O39" t="s" s="2">
+        <v>337</v>
+      </c>
+      <c r="P39" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q39" s="2"/>
+      <c r="R39" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S39" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T39" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U39" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V39" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W39" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X39" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y39" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z39" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA39" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB39" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC39" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD39" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE39" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF39" t="s" s="2">
+        <v>338</v>
+      </c>
+      <c r="AG39" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH39" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI39" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ39" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK39" t="s" s="2">
+        <v>339</v>
+      </c>
+      <c r="AL39" t="s" s="2">
+        <v>340</v>
+      </c>
+      <c r="AM39" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN39" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="s" s="2">
+        <v>341</v>
+      </c>
+      <c r="B40" t="s" s="2">
+        <v>341</v>
+      </c>
+      <c r="C40" s="2"/>
+      <c r="D40" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E40" s="2"/>
+      <c r="F40" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G40" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H40" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="I40" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J40" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="K40" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="L40" t="s" s="2">
+        <v>342</v>
+      </c>
+      <c r="M40" t="s" s="2">
+        <v>343</v>
+      </c>
+      <c r="N40" t="s" s="2">
+        <v>344</v>
+      </c>
+      <c r="O40" t="s" s="2">
+        <v>345</v>
+      </c>
+      <c r="P40" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q40" s="2"/>
+      <c r="R40" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S40" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T40" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U40" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V40" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W40" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X40" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y40" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z40" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA40" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB40" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC40" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD40" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE40" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF40" t="s" s="2">
+        <v>346</v>
+      </c>
+      <c r="AG40" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH40" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI40" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ40" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK40" t="s" s="2">
+        <v>347</v>
+      </c>
+      <c r="AL40" t="s" s="2">
+        <v>348</v>
+      </c>
+      <c r="AM40" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN40" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="41" hidden="true">
+      <c r="A41" t="s" s="2">
+        <v>349</v>
+      </c>
+      <c r="B41" t="s" s="2">
+        <v>349</v>
+      </c>
+      <c r="C41" s="2"/>
+      <c r="D41" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E41" s="2"/>
+      <c r="F41" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G41" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H41" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I41" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J41" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K41" t="s" s="2">
+        <v>253</v>
+      </c>
+      <c r="L41" t="s" s="2">
+        <v>350</v>
+      </c>
+      <c r="M41" t="s" s="2">
+        <v>351</v>
+      </c>
+      <c r="N41" s="2"/>
+      <c r="O41" t="s" s="2">
+        <v>352</v>
+      </c>
+      <c r="P41" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q41" s="2"/>
+      <c r="R41" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S41" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T41" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U41" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V41" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W41" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X41" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y41" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z41" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA41" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB41" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC41" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD41" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE41" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF41" t="s" s="2">
+        <v>349</v>
+      </c>
+      <c r="AG41" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH41" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI41" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ41" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK41" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL41" t="s" s="2">
+        <v>353</v>
+      </c>
+      <c r="AM41" t="s" s="2">
+        <v>354</v>
+      </c>
+      <c r="AN41" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="42" hidden="true">
+      <c r="A42" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="B42" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="C42" s="2"/>
+      <c r="D42" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E42" s="2"/>
+      <c r="F42" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G42" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H42" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I42" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J42" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K42" t="s" s="2">
+        <v>356</v>
+      </c>
+      <c r="L42" t="s" s="2">
+        <v>357</v>
+      </c>
+      <c r="M42" t="s" s="2">
+        <v>358</v>
+      </c>
+      <c r="N42" s="2"/>
+      <c r="O42" s="2"/>
+      <c r="P42" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q42" s="2"/>
+      <c r="R42" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S42" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T42" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U42" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V42" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W42" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X42" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y42" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z42" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA42" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB42" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC42" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD42" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE42" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF42" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="AG42" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH42" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI42" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ42" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK42" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL42" t="s" s="2">
+        <v>359</v>
+      </c>
+      <c r="AM42" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN42" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="s" s="2">
+        <v>360</v>
+      </c>
+      <c r="B43" t="s" s="2">
+        <v>360</v>
+      </c>
+      <c r="C43" s="2"/>
+      <c r="D43" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E43" s="2"/>
+      <c r="F43" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G43" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H43" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="I43" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J43" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K43" t="s" s="2">
+        <v>323</v>
+      </c>
+      <c r="L43" t="s" s="2">
+        <v>361</v>
+      </c>
+      <c r="M43" t="s" s="2">
+        <v>362</v>
+      </c>
+      <c r="N43" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="O43" t="s" s="2">
+        <v>364</v>
+      </c>
+      <c r="P43" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q43" s="2"/>
+      <c r="R43" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S43" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T43" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U43" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V43" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W43" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X43" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="Y43" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="Z43" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="AA43" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB43" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC43" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD43" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE43" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF43" t="s" s="2">
+        <v>360</v>
+      </c>
+      <c r="AG43" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH43" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI43" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ43" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK43" t="s" s="2">
+        <v>365</v>
+      </c>
+      <c r="AL43" t="s" s="2">
+        <v>366</v>
+      </c>
+      <c r="AM43" t="s" s="2">
+        <v>367</v>
+      </c>
+      <c r="AN43" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="44" hidden="true">
+      <c r="A44" t="s" s="2">
+        <v>368</v>
+      </c>
+      <c r="B44" t="s" s="2">
+        <v>368</v>
+      </c>
+      <c r="C44" s="2"/>
+      <c r="D44" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E44" s="2"/>
+      <c r="F44" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G44" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H44" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I44" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J44" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K44" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="L44" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="M44" t="s" s="2">
+        <v>193</v>
+      </c>
+      <c r="N44" s="2"/>
+      <c r="O44" s="2"/>
+      <c r="P44" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q44" s="2"/>
+      <c r="R44" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S44" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T44" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U44" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V44" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W44" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X44" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y44" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z44" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA44" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB44" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC44" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD44" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE44" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF44" t="s" s="2">
+        <v>194</v>
+      </c>
+      <c r="AG44" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH44" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI44" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ44" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AK44" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL44" t="s" s="2">
+        <v>195</v>
+      </c>
+      <c r="AM44" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN44" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="45" hidden="true">
+      <c r="A45" t="s" s="2">
+        <v>369</v>
+      </c>
+      <c r="B45" t="s" s="2">
+        <v>369</v>
+      </c>
+      <c r="C45" s="2"/>
+      <c r="D45" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="E45" s="2"/>
+      <c r="F45" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G45" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H45" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I45" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J45" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K45" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="L45" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="M45" t="s" s="2">
+        <v>198</v>
+      </c>
+      <c r="N45" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="O45" s="2"/>
+      <c r="P45" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q45" s="2"/>
+      <c r="R45" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S45" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T45" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U45" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V45" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W45" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X45" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y45" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z45" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA45" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB45" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="AC45" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="AD45" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE45" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="AF45" t="s" s="2">
+        <v>200</v>
+      </c>
+      <c r="AG45" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH45" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI45" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ45" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="AK45" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL45" t="s" s="2">
+        <v>195</v>
+      </c>
+      <c r="AM45" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN45" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="s" s="2">
+        <v>370</v>
+      </c>
+      <c r="B46" t="s" s="2">
+        <v>370</v>
+      </c>
+      <c r="C46" s="2"/>
+      <c r="D46" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E46" s="2"/>
+      <c r="F46" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G46" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H46" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="I46" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J46" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="K46" t="s" s="2">
+        <v>333</v>
+      </c>
+      <c r="L46" t="s" s="2">
+        <v>334</v>
+      </c>
+      <c r="M46" t="s" s="2">
+        <v>335</v>
+      </c>
+      <c r="N46" t="s" s="2">
+        <v>336</v>
+      </c>
+      <c r="O46" t="s" s="2">
+        <v>337</v>
+      </c>
+      <c r="P46" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q46" s="2"/>
+      <c r="R46" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S46" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T46" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U46" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V46" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W46" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X46" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y46" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z46" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA46" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB46" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC46" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD46" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE46" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF46" t="s" s="2">
+        <v>338</v>
+      </c>
+      <c r="AG46" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH46" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI46" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ46" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK46" t="s" s="2">
+        <v>339</v>
+      </c>
+      <c r="AL46" t="s" s="2">
+        <v>340</v>
+      </c>
+      <c r="AM46" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN46" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="s" s="2">
+        <v>371</v>
+      </c>
+      <c r="B47" t="s" s="2">
+        <v>371</v>
+      </c>
+      <c r="C47" s="2"/>
+      <c r="D47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E47" s="2"/>
+      <c r="F47" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G47" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H47" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="I47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J47" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="K47" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="L47" t="s" s="2">
+        <v>342</v>
+      </c>
+      <c r="M47" t="s" s="2">
+        <v>343</v>
+      </c>
+      <c r="N47" t="s" s="2">
+        <v>344</v>
+      </c>
+      <c r="O47" t="s" s="2">
+        <v>345</v>
+      </c>
+      <c r="P47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q47" s="2"/>
+      <c r="R47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF47" t="s" s="2">
+        <v>346</v>
+      </c>
+      <c r="AG47" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH47" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ47" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK47" t="s" s="2">
+        <v>347</v>
+      </c>
+      <c r="AL47" t="s" s="2">
+        <v>348</v>
+      </c>
+      <c r="AM47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN47" t="s" s="2">
         <v>77</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AN35">
+  <autoFilter ref="A1:AN47">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -5318,7 +6918,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI34">
+  <conditionalFormatting sqref="A2:AI46">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/dev/StructureDefinition-ph-core-practitioner.xlsx
+++ b/dev/StructureDefinition-ph-core-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-26T03:51:01+00:00</t>
+    <t>2026-05-26T04:00:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/StructureDefinition-ph-core-practitioner.xlsx
+++ b/dev/StructureDefinition-ph-core-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-26T04:00:40+00:00</t>
+    <t>2026-05-26T04:36:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
